--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487177_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487177_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.037800000000001</v>
+        <v>8.5108</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8477</v>
+        <v>6.508</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1902</v>
+        <v>2.0028</v>
       </c>
       <c r="G2" t="n">
         <v>6.562</v>
@@ -610,13 +610,13 @@
         <v>0.965</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2479</v>
+        <v>0.7208</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2829</v>
+        <v>0.3774</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.3434</v>
       </c>
       <c r="V2" t="n">
         <v>1.228</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.4079</v>
+        <v>7.4127</v>
       </c>
       <c r="E3" t="n">
-        <v>8.8986</v>
+        <v>6.1722</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4907</v>
+        <v>1.2406</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2727</v>
+        <v>7.2157</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6116</v>
+        <v>3.7156</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6612</v>
+        <v>3.5001</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1947</v>
+        <v>7.8292</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5667</v>
+        <v>4.0363</v>
       </c>
       <c r="L3" t="n">
-        <v>1.628</v>
+        <v>3.7929</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9219</v>
+        <v>-0.6135</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9550999999999999</v>
+        <v>-0.3207</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9668</v>
+        <v>-0.2928</v>
       </c>
       <c r="P3" t="n">
-        <v>0.579</v>
+        <v>-0.579</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.158</v>
+        <v>-2.1231</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7371</v>
+        <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>6.7262</v>
+        <v>1.0619</v>
       </c>
       <c r="T3" t="n">
-        <v>5.5762</v>
+        <v>0.466</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1501</v>
+        <v>0.5959</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1701</v>
+        <v>-0.2859</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.4559</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.8525</v>
+        <v>3.7206</v>
       </c>
       <c r="E4" t="n">
-        <v>5.8529</v>
+        <v>5.8538</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9996</v>
+        <v>-2.1332</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2157</v>
+        <v>2.2727</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7156</v>
+        <v>1.6116</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5001</v>
+        <v>0.6612</v>
       </c>
       <c r="J4" t="n">
-        <v>7.8292</v>
+        <v>4.1947</v>
       </c>
       <c r="K4" t="n">
-        <v>4.0363</v>
+        <v>2.5667</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7929</v>
+        <v>1.628</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6135</v>
+        <v>-1.9219</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3207</v>
+        <v>-0.9550999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2928</v>
+        <v>-0.9668</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.579</v>
+        <v>0.579</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5017</v>
+        <v>3.0389</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1468</v>
+        <v>2.5313</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3549</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2859</v>
+        <v>-2.1701</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5514</v>
+        <v>3.4235</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2938</v>
+        <v>1.1123</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2576</v>
+        <v>2.3112</v>
       </c>
       <c r="G5" t="n">
         <v>3.0661</v>
@@ -844,13 +844,13 @@
         <v>1.3511</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3622</v>
+        <v>0.2343</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1322</v>
+        <v>-0.0492</v>
       </c>
       <c r="U5" t="n">
-        <v>0.23</v>
+        <v>0.2835</v>
       </c>
       <c r="V5" t="n">
         <v>-1.228</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>S. JOKSIMOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5403</v>
+        <v>2.9569</v>
       </c>
       <c r="E6" t="n">
-        <v>5.1197</v>
+        <v>1.6758</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5794</v>
+        <v>1.2811</v>
       </c>
       <c r="G6" t="n">
-        <v>4.5529</v>
+        <v>2.0879</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0146</v>
+        <v>1.6145</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5383</v>
+        <v>0.4734</v>
       </c>
       <c r="J6" t="n">
-        <v>4.613</v>
+        <v>2.0547</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2018</v>
+        <v>1.9819</v>
       </c>
       <c r="L6" t="n">
-        <v>4.4112</v>
+        <v>0.0728</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0601</v>
+        <v>0.0332</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1872</v>
+        <v>-0.3674</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1271</v>
+        <v>0.4006</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4131</v>
+        <v>0.1742</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2208</v>
+        <v>0.2773</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1923</v>
+        <v>-0.1031</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.9698</v>
+        <v>-0.6562</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2859</v>
+        <v>-0.6562</v>
       </c>
       <c r="X6" t="n">
-        <v>-4.2556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. JOKSIMOVIC</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3968</v>
+        <v>2.8389</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1156</v>
+        <v>0.4723</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2811</v>
+        <v>2.3666</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0879</v>
+        <v>1.087</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6145</v>
+        <v>0.3137</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4734</v>
+        <v>0.7733</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0547</v>
+        <v>1.1267</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9819</v>
+        <v>0.207</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0728</v>
+        <v>0.9197</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0332</v>
+        <v>-0.0397</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3674</v>
+        <v>0.1067</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4006</v>
+        <v>-0.1464</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3511</v>
+        <v>1.9301</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.386</v>
+        <v>0.7869</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2829</v>
+        <v>0.3107</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1031</v>
+        <v>0.4762</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1915</v>
+        <v>2.7059</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0122</v>
+        <v>5.5797</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1792</v>
+        <v>-2.8738</v>
       </c>
       <c r="G8" t="n">
-        <v>1.087</v>
+        <v>4.5529</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3137</v>
+        <v>0.0146</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7733</v>
+        <v>4.5383</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1267</v>
+        <v>4.613</v>
       </c>
       <c r="K8" t="n">
-        <v>0.207</v>
+        <v>0.2018</v>
       </c>
       <c r="L8" t="n">
-        <v>0.9197</v>
+        <v>4.4112</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0397</v>
+        <v>-0.0601</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1067</v>
+        <v>-0.1872</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1464</v>
+        <v>0.1271</v>
       </c>
       <c r="P8" t="n">
-        <v>0.965</v>
+        <v>1.5441</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1395</v>
+        <v>0.5787</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>0.6808</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2888</v>
+        <v>-0.1021</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-3.9698</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-4.2556</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. MIGUEL PEREZ DEL NOTARIO</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4076</v>
+        <v>1.8353</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1316</v>
+        <v>0.9696</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.724</v>
+        <v>0.8657</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0114</v>
+        <v>0.5513</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5755</v>
+        <v>0.3528</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4359</v>
+        <v>0.1985</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9647</v>
+        <v>1.5252</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6624</v>
+        <v>0.7604</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3024</v>
+        <v>0.7647</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0466</v>
+        <v>-0.9739</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.4076</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1335</v>
+        <v>-0.5662</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.579</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.7371</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2756</v>
+        <v>0.9908</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.119</v>
+        <v>0.6025</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1567</v>
+        <v>0.3883</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3281</v>
+        <v>-0.2859</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.614</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>E. MIGUEL PEREZ DEL NOTARIO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7605</v>
+        <v>1.5276</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3499</v>
+        <v>2.3319</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4106</v>
+        <v>-0.8043</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5513</v>
+        <v>2.0114</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3528</v>
+        <v>0.5755</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1985</v>
+        <v>1.4359</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5252</v>
+        <v>1.9647</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7604</v>
+        <v>0.6624</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7647</v>
+        <v>1.3024</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9739</v>
+        <v>0.0466</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4076</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5662</v>
+        <v>0.1335</v>
       </c>
       <c r="P10" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7371</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0839</v>
+        <v>-0.1557</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0172</v>
+        <v>0.0813</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0668</v>
+        <v>-0.237</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2859</v>
+        <v>-0.3281</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2859</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0693</v>
+        <v>0.4163</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.045</v>
+        <v>0.1146</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1143</v>
+        <v>0.3017</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4374</v>
@@ -1312,13 +1312,13 @@
         <v>0.772</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2135</v>
+        <v>0.5605</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1917</v>
+        <v>0.3513</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0218</v>
+        <v>0.2092</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2859</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2133</v>
+        <v>-0.6997</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4328</v>
+        <v>0.8928</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6461</v>
+        <v>-1.5925</v>
       </c>
       <c r="G12" t="n">
         <v>0.3693</v>
@@ -1390,13 +1390,13 @@
         <v>0.386</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4548</v>
+        <v>0.0588</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2234</v>
+        <v>0.2366</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2313</v>
+        <v>-0.1778</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5138</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3802</v>
+        <v>-2.1343</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6538</v>
+        <v>-2.4347</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2736</v>
+        <v>0.3003</v>
       </c>
       <c r="G13" t="n">
         <v>0.3924</v>
@@ -1468,13 +1468,13 @@
         <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7595</v>
+        <v>1.0054</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6504</v>
+        <v>0.8696</v>
       </c>
       <c r="U13" t="n">
-        <v>0.109</v>
+        <v>0.1358</v>
       </c>
       <c r="V13" t="n">
         <v>0.3281</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>31.62210000000001</v>
+        <v>32.5145</v>
       </c>
       <c r="E14" t="n">
-        <v>28.356</v>
+        <v>29.2483</v>
       </c>
       <c r="F14" t="n">
-        <v>3.266</v>
+        <v>3.2662</v>
       </c>
       <c r="G14" t="n">
-        <v>29.7313</v>
+        <v>29.73129999999999</v>
       </c>
       <c r="H14" t="n">
         <v>12.7198</v>
@@ -1546,13 +1546,13 @@
         <v>15.4408</v>
       </c>
       <c r="S14" t="n">
-        <v>8.1633</v>
+        <v>9.0555</v>
       </c>
       <c r="T14" t="n">
-        <v>5.843300000000001</v>
+        <v>6.7356</v>
       </c>
       <c r="U14" t="n">
-        <v>2.319699999999999</v>
+        <v>2.3199</v>
       </c>
       <c r="V14" t="n">
         <v>-9.167600000000002</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2627</v>
+        <v>2.8166</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1515</v>
+        <v>3.6522</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8888</v>
+        <v>-0.8356</v>
       </c>
       <c r="G15" t="n">
         <v>0.6676</v>
@@ -1624,13 +1624,13 @@
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4628</v>
+        <v>-0.9089</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9518</v>
+        <v>-0.4511</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.511</v>
+        <v>-0.4578</v>
       </c>
       <c r="V15" t="n">
         <v>1.5138</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8167</v>
+        <v>1.0907</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1971</v>
+        <v>2.097</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3804</v>
+        <v>-1.0063</v>
       </c>
       <c r="G16" t="n">
         <v>1.2939</v>
@@ -1702,13 +1702,13 @@
         <v>0.193</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4772</v>
+        <v>-0.2033</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4297</v>
+        <v>0.3295</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9069</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ALLAS MENESES</t>
+          <t>I. HERRERO PERAL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0306</v>
+        <v>-2.0653</v>
       </c>
       <c r="E17" t="n">
-        <v>2.009</v>
+        <v>-1.0092</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.0396</v>
+        <v>-1.0561</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.1441</v>
+        <v>-1.6862</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.162</v>
+        <v>-0.4067</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.9821</v>
+        <v>-1.2795</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5127</v>
+        <v>0.4695</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2588</v>
+        <v>1.0557</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2538</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.6315</v>
+        <v>-2.1557</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.9032</v>
+        <v>-1.4624</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.7283</v>
+        <v>-0.6933</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>0.386</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4297</v>
+        <v>-0.7651</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5169</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0873</v>
+        <v>-0.2515</v>
       </c>
       <c r="V17" t="n">
-        <v>3.6839</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.9698</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. HERRERO PERAL</t>
+          <t>A. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3994</v>
+        <v>-2.598</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2094</v>
+        <v>1.308</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.19</v>
+        <v>-3.9061</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6862</v>
+        <v>-6.1441</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4067</v>
+        <v>-2.162</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2795</v>
+        <v>-3.9821</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4695</v>
+        <v>-1.5127</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0557</v>
+        <v>-0.2588</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-1.2538</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1557</v>
+        <v>-4.6315</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4624</v>
+        <v>-1.9032</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6933</v>
+        <v>-2.7283</v>
       </c>
       <c r="P18" t="n">
-        <v>0.386</v>
+        <v>-0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0992</v>
+        <v>-0.1378</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7139</v>
+        <v>-0.1841</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3854</v>
+        <v>0.0462</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>3.6839</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.9698</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.8984</v>
+        <v>-3.204</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5456</v>
+        <v>1.9462</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.444</v>
+        <v>-5.1502</v>
       </c>
       <c r="G19" t="n">
         <v>-5.0372</v>
@@ -1936,13 +1936,13 @@
         <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0312</v>
+        <v>-1.3368</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2942</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.737</v>
+        <v>-0.4432</v>
       </c>
       <c r="V19" t="n">
         <v>2.784</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.1277</v>
+        <v>-5.5415</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0348</v>
+        <v>-2.6356</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0929</v>
+        <v>-2.9059</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8775</v>
@@ -2014,13 +2014,13 @@
         <v>1.7371</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5288</v>
+        <v>-0.9426</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3239</v>
+        <v>-0.2769</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8527</v>
+        <v>-0.6656</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3704</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ALLAS MENESES</t>
+          <t>M. HERRERO CRESPO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.6378</v>
+        <v>-6.2377</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9775</v>
+        <v>-2.6999</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.6603</v>
+        <v>-3.5378</v>
       </c>
       <c r="G21" t="n">
-        <v>-4.3113</v>
+        <v>-3.6469</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9964</v>
+        <v>1.3477</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3149</v>
+        <v>-4.9946</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9212</v>
+        <v>1.2442</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9212</v>
+        <v>3.0842</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-1.84</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.3901</v>
+        <v>-4.891</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0752</v>
+        <v>-1.7365</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.3149</v>
+        <v>-3.1546</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.158</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9301</v>
+        <v>-4.0532</v>
       </c>
       <c r="R21" t="n">
-        <v>0.772</v>
+        <v>1.9301</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6736</v>
+        <v>-1.124</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8739</v>
+        <v>-0.1768</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2003</v>
+        <v>-0.9472</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.842</v>
+        <v>0.6562</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.842</v>
+        <v>0.3704</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.7866</v>
+        <v>-6.8282</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5468</v>
+        <v>-3.3465</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2398</v>
+        <v>-3.4817</v>
       </c>
       <c r="G22" t="n">
         <v>-7.9896</v>
@@ -2170,13 +2170,13 @@
         <v>2.5091</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9598</v>
+        <v>-1.0014</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6266</v>
+        <v>-0.4263</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3332</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>2.7418</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. HERRERO CRESPO</t>
+          <t>D. ALLAS MENESES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.8211</v>
+        <v>-7.0519</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4009</v>
+        <v>-2.5783</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.4202</v>
+        <v>-4.4736</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6469</v>
+        <v>-4.3113</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3477</v>
+        <v>-1.9964</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.9946</v>
+        <v>-2.3149</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2442</v>
+        <v>-0.9212</v>
       </c>
       <c r="K23" t="n">
-        <v>3.0842</v>
+        <v>-0.9212</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.84</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.891</v>
+        <v>-3.3901</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7365</v>
+        <v>-1.0752</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.1546</v>
+        <v>-2.3149</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.0532</v>
+        <v>-1.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9301</v>
+        <v>0.772</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.7074</v>
+        <v>0.2594</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8778</v>
+        <v>0.273</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.8296</v>
+        <v>-0.0136</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6562</v>
+        <v>-1.842</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3704</v>
+        <v>-1.842</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-31.6222</v>
+        <v>-29.6193</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.266200000000001</v>
+        <v>-3.2661</v>
       </c>
       <c r="F24" t="n">
-        <v>-28.356</v>
+        <v>-26.3533</v>
       </c>
       <c r="G24" t="n">
         <v>-29.7313</v>
@@ -2305,7 +2305,7 @@
         <v>2.5399</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8284</v>
+        <v>0.8283999999999996</v>
       </c>
       <c r="M24" t="n">
         <v>-33.0993</v>
@@ -2326,13 +2326,13 @@
         <v>12.5456</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.1631</v>
+        <v>-6.1605</v>
       </c>
       <c r="T24" t="n">
         <v>-2.3199</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.8434</v>
+        <v>-3.8406</v>
       </c>
       <c r="V24" t="n">
         <v>9.167299999999999</v>
